--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487987_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487987_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.425</v>
+        <v>10.7068</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0534</v>
+        <v>8.5318</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3716</v>
+        <v>2.175</v>
       </c>
       <c r="G2" t="n">
         <v>3.2175</v>
@@ -610,13 +610,13 @@
         <v>2.5769</v>
       </c>
       <c r="S2" t="n">
-        <v>4.777</v>
+        <v>3.0588</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6932</v>
+        <v>2.1715</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0838</v>
+        <v>0.8873</v>
       </c>
       <c r="V2" t="n">
         <v>3.0429</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0422</v>
+        <v>3.3165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9813</v>
+        <v>0.761</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0609</v>
+        <v>2.5555</v>
       </c>
       <c r="G3" t="n">
         <v>-1.8584</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9616</v>
+        <v>3.2359</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6579</v>
+        <v>2.4376</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3037</v>
+        <v>0.7982</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2414</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1185</v>
+        <v>2.9626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9638</v>
+        <v>0.7026</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1548</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6991</v>
+        <v>0.2761</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3868</v>
+        <v>-1.6314</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0859</v>
+        <v>1.9075</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0135</v>
+        <v>1.5877</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5177</v>
+        <v>1.0498</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5312</v>
+        <v>0.5379</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3144</v>
+        <v>-1.3115</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8691</v>
+        <v>-2.6812</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5547</v>
+        <v>1.3697</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3876</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-4.1627</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3787</v>
+        <v>3.7662</v>
       </c>
       <c r="S4" t="n">
-        <v>0.239</v>
+        <v>2.1172</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0586</v>
+        <v>1.5374</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2976</v>
+        <v>0.5798</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2071</v>
+        <v>0.9657</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2071</v>
+        <v>-0.7746</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2845</v>
+        <v>2.5375</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5262</v>
+        <v>1.3547</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8107</v>
+        <v>1.1828</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2761</v>
+        <v>1.6991</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6314</v>
+        <v>-1.3868</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9075</v>
+        <v>3.0859</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5877</v>
+        <v>2.0135</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0498</v>
+        <v>-0.5177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5379</v>
+        <v>2.5312</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3115</v>
+        <v>-0.3144</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.6812</v>
+        <v>-0.8691</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3697</v>
+        <v>0.5547</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1627</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7662</v>
+        <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4391</v>
+        <v>0.658</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3085</v>
+        <v>0.3323</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1306</v>
+        <v>0.3257</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9657</v>
+        <v>-1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7746</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7929</v>
+        <v>1.865</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7767</v>
+        <v>1.662</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5696</v>
+        <v>0.203</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6286</v>
+        <v>0.618</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7141</v>
+        <v>-0.7214</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9145</v>
+        <v>1.3393</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5198</v>
+        <v>1.9274</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3568</v>
+        <v>2.6311</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8767</v>
+        <v>-0.7037</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1087</v>
+        <v>-1.3094</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0709</v>
+        <v>-3.3525</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9622000000000001</v>
+        <v>2.0431</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5769</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1982</v>
+        <v>-4.1627</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7751</v>
+        <v>3.7662</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3777</v>
+        <v>2.2218</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0586</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4363</v>
+        <v>0.4018</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5331</v>
+        <v>-0.5784</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5331</v>
+        <v>-2.6556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. KOROL</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5417999999999999</v>
+        <v>1.0144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0352</v>
+        <v>-1.5271</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5066000000000001</v>
+        <v>2.5415</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9058</v>
+        <v>-1.6286</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6279</v>
+        <v>-0.7141</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2779</v>
+        <v>-0.9145</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3782</v>
+        <v>-1.5198</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5788</v>
+        <v>0.3568</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.957</v>
+        <v>-1.8767</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5276</v>
+        <v>-0.1087</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2067</v>
+        <v>-1.0709</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6791</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>2.7751</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1012</v>
+        <v>0.5992</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4134</v>
+        <v>0.191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6878</v>
+        <v>0.4083</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0411</v>
+        <v>-0.5331</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0411</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>N. KOROL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3391</v>
+        <v>0.1301</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0367</v>
+        <v>-0.208</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3024</v>
+        <v>0.3382</v>
       </c>
       <c r="G8" t="n">
-        <v>0.618</v>
+        <v>-1.9058</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7214</v>
+        <v>-0.6279</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3393</v>
+        <v>-1.2779</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9274</v>
+        <v>-1.3782</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6311</v>
+        <v>0.5788</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7037</v>
+        <v>-1.957</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3094</v>
+        <v>-0.5276</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.3525</v>
+        <v>-1.2067</v>
       </c>
       <c r="O8" t="n">
-        <v>2.0431</v>
+        <v>0.6791</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.7662</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0177</v>
+        <v>1.6896</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1213</v>
+        <v>1.1702</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1036</v>
+        <v>0.5193</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5784</v>
+        <v>-1.0411</v>
       </c>
       <c r="W8" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6556</v>
+        <v>-1.0411</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4517</v>
+        <v>-3.1459</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8837</v>
+        <v>-2.6341</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5679</v>
+        <v>-0.5118</v>
       </c>
       <c r="G9" t="n">
         <v>-5.2172</v>
@@ -1156,13 +1156,13 @@
         <v>2.3787</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1975</v>
+        <v>1.5032</v>
       </c>
       <c r="T9" t="n">
-        <v>1.351</v>
+        <v>1.6006</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1535</v>
+        <v>-0.0974</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8107</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5401</v>
+        <v>-3.329</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1871</v>
+        <v>-3.8357</v>
       </c>
       <c r="F10" t="n">
-        <v>0.647</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7763</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5745</v>
+        <v>-0.3634</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5616</v>
+        <v>-0.2101</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0129</v>
+        <v>-0.1533</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.874</v>
+        <v>16.058</v>
       </c>
       <c r="E11" t="n">
-        <v>2.623299999999999</v>
+        <v>4.807199999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>11.2509</v>
+        <v>11.2508</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5756</v>
+        <v>-5.575600000000001</v>
       </c>
       <c r="H11" t="n">
         <v>-11.5451</v>
@@ -1291,7 +1291,7 @@
         <v>4.5379</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.274300000000001</v>
+        <v>-4.2743</v>
       </c>
       <c r="M11" t="n">
         <v>-5.8392</v>
@@ -1312,13 +1312,13 @@
         <v>22.7957</v>
       </c>
       <c r="S11" t="n">
-        <v>12.5363</v>
+        <v>14.7203</v>
       </c>
       <c r="T11" t="n">
-        <v>8.8665</v>
+        <v>11.0505</v>
       </c>
       <c r="U11" t="n">
-        <v>3.6698</v>
+        <v>3.669700000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0068</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3354</v>
+        <v>1.4679</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7857</v>
+        <v>1.0913</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5497</v>
+        <v>0.3766</v>
       </c>
       <c r="G12" t="n">
         <v>1.7591</v>
@@ -1390,13 +1390,13 @@
         <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8799</v>
+        <v>-1.7474</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0608</v>
+        <v>-0.7551</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8192</v>
+        <v>-0.9922</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7243000000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2356</v>
+        <v>1.086</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1085</v>
+        <v>0.489</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1271</v>
+        <v>0.597</v>
       </c>
       <c r="G13" t="n">
-        <v>4.0244</v>
+        <v>-0.0585</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0478</v>
+        <v>1.4739</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0234</v>
+        <v>-1.5325</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0947</v>
+        <v>-0.235</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8313</v>
+        <v>1.722</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7367</v>
+        <v>-1.957</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0702</v>
+        <v>0.1765</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7836</v>
+        <v>-0.2481</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7133</v>
+        <v>0.4246</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.7751</v>
+        <v>1.3876</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1538</v>
+        <v>-0.1982</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3787</v>
+        <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9512</v>
+        <v>-1.3968</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2975</v>
+        <v>-0.5514</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2487</v>
+        <v>-0.8454</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9375</v>
+        <v>1.1538</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8701</v>
+        <v>1.4737</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0674</v>
+        <v>-0.3199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.7569</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.1971</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6052999999999999</v>
+        <v>4.0244</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6052999999999999</v>
+        <v>5.0478</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1.0234</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6052999999999999</v>
+        <v>4.0947</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6052999999999999</v>
+        <v>5.8313</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.7367</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.0702</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.7836</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.7133</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-5.1538</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-1.4299</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.0081</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-1.4218</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5486</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0203</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5689</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0585</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4739</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5325</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.235</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>1.722</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.957</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2481</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4246</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9342</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0608</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1538</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2244</v>
+        <v>0.2525</v>
       </c>
       <c r="E16" t="n">
         <v>-0.1248</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3492</v>
+        <v>0.3773</v>
       </c>
       <c r="G16" t="n">
         <v>0.2057</v>
@@ -1702,13 +1702,13 @@
         <v>0.1982</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1795</v>
+        <v>-0.1514</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0547</v>
+        <v>-0.0266</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6557</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7589</v>
+        <v>-1.5551</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1032</v>
+        <v>0.604</v>
       </c>
       <c r="G17" t="n">
         <v>1.1118</v>
@@ -1780,13 +1780,13 @@
         <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1977</v>
+        <v>-1.4931</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1232</v>
+        <v>-0.9194</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0746</v>
+        <v>-0.5737</v>
       </c>
       <c r="V17" t="n">
         <v>1.016</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6961</v>
+        <v>-1.9384</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2767</v>
+        <v>0.1748</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9728</v>
+        <v>-2.1132</v>
       </c>
       <c r="G18" t="n">
         <v>0.9123</v>
@@ -1858,13 +1858,13 @@
         <v>0.3964</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2001</v>
+        <v>-0.4424</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0552</v>
+        <v>-0.0467</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2553</v>
+        <v>-0.3957</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8137</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7297</v>
+        <v>-2.1477</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0582</v>
+        <v>-1.3639</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6715</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9044</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0235</v>
+        <v>-0.4414</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0552</v>
+        <v>-0.2505</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.191</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9137</v>
+        <v>-2.5533</v>
       </c>
       <c r="E20" t="n">
         <v>-2.8326</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.2793</v>
       </c>
       <c r="G20" t="n">
         <v>0.6304999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.251</v>
+        <v>-1.8905</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3816</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8694</v>
+        <v>-1.5089</v>
       </c>
       <c r="V20" t="n">
         <v>0.8872</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9537</v>
+        <v>-4.0392</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7007</v>
+        <v>-2.0063</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2529</v>
+        <v>-2.0329</v>
       </c>
       <c r="G21" t="n">
         <v>0.9092</v>
@@ -2092,13 +2092,13 @@
         <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0194</v>
+        <v>-1.105</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0552</v>
+        <v>-0.2505</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0746</v>
+        <v>-0.8545</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8701</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.8743</v>
+        <v>-5.734</v>
       </c>
       <c r="E22" t="n">
         <v>-6.1351</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2608</v>
+        <v>0.4012</v>
       </c>
       <c r="G22" t="n">
         <v>-3.6199</v>
@@ -2170,13 +2170,13 @@
         <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8997</v>
+        <v>-1.7593</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3816</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.518</v>
+        <v>-1.3777</v>
       </c>
       <c r="V22" t="n">
         <v>2.0239</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-13.8739</v>
+        <v>-13.1951</v>
       </c>
       <c r="E23" t="n">
-        <v>-11.8544</v>
+        <v>-11.8545</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0195</v>
+        <v>-1.3404</v>
       </c>
       <c r="G23" t="n">
-        <v>5.575500000000002</v>
+        <v>5.5755</v>
       </c>
       <c r="H23" t="n">
         <v>11.5452</v>
@@ -2248,13 +2248,13 @@
         <v>13.8756</v>
       </c>
       <c r="S23" t="n">
-        <v>-12.5362</v>
+        <v>-11.8572</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.6697</v>
+        <v>-3.669700000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-8.8667</v>
+        <v>-8.1875</v>
       </c>
       <c r="V23" t="n">
         <v>2.0067</v>
